--- a/data/nzd0123/nzd0123.xlsx
+++ b/data/nzd0123/nzd0123.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H638"/>
+  <dimension ref="A1:H639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19578,6 +19578,36 @@
       <c r="H638" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>351.95</v>
+      </c>
+      <c r="C639" t="n">
+        <v>346.79</v>
+      </c>
+      <c r="D639" t="n">
+        <v>359.72</v>
+      </c>
+      <c r="E639" t="n">
+        <v>368.84</v>
+      </c>
+      <c r="F639" t="n">
+        <v>383.04</v>
+      </c>
+      <c r="G639" t="n">
+        <v>360.99</v>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -19592,7 +19622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B665"/>
+  <dimension ref="A1:B666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26245,6 +26275,16 @@
       </c>
       <c r="B665" t="n">
         <v>0.63</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="n">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>
@@ -26413,28 +26453,28 @@
         <v>0.0654</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1128911899112311</v>
+        <v>0.1094646308787722</v>
       </c>
       <c r="J2" t="n">
+        <v>638</v>
+      </c>
+      <c r="K2" t="n">
         <v>637</v>
       </c>
-      <c r="K2" t="n">
-        <v>636</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02914366529727708</v>
+        <v>0.02734082725822695</v>
       </c>
       <c r="M2" t="n">
-        <v>3.860964428431728</v>
+        <v>3.870142980548304</v>
       </c>
       <c r="N2" t="n">
-        <v>23.0058751728948</v>
+        <v>23.14652338184678</v>
       </c>
       <c r="O2" t="n">
-        <v>4.796444013318075</v>
+        <v>4.811083389616811</v>
       </c>
       <c r="P2" t="n">
-        <v>359.6246462902412</v>
+        <v>359.6598335954529</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26491,28 +26531,28 @@
         <v>0.0953</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2047947063650452</v>
+        <v>0.2010910058217201</v>
       </c>
       <c r="J3" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="K3" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05668974988781605</v>
+        <v>0.05467339451625619</v>
       </c>
       <c r="M3" t="n">
-        <v>5.224214237043656</v>
+        <v>5.231466882372998</v>
       </c>
       <c r="N3" t="n">
-        <v>37.7618421934074</v>
+        <v>37.90877898571216</v>
       </c>
       <c r="O3" t="n">
-        <v>6.145066492187647</v>
+        <v>6.15701055592015</v>
       </c>
       <c r="P3" t="n">
-        <v>352.9023545982633</v>
+        <v>352.9404085690507</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26569,28 +26609,28 @@
         <v>0.1104</v>
       </c>
       <c r="I4" t="n">
-        <v>0.274400612435616</v>
+        <v>0.2709101186032515</v>
       </c>
       <c r="J4" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="K4" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1364844416184346</v>
+        <v>0.133092019670116</v>
       </c>
       <c r="M4" t="n">
-        <v>4.077010293486482</v>
+        <v>4.085041245138786</v>
       </c>
       <c r="N4" t="n">
-        <v>25.77643661205326</v>
+        <v>25.91911088423081</v>
       </c>
       <c r="O4" t="n">
-        <v>5.07704999109259</v>
+        <v>5.091081504379086</v>
       </c>
       <c r="P4" t="n">
-        <v>363.346406354135</v>
+        <v>363.3822697153264</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26647,28 +26687,28 @@
         <v>0.0921</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1845117624135373</v>
+        <v>0.1821929597794094</v>
       </c>
       <c r="J5" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="K5" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06299183764835814</v>
+        <v>0.06155300352278059</v>
       </c>
       <c r="M5" t="n">
-        <v>4.041927680253651</v>
+        <v>4.045774873749763</v>
       </c>
       <c r="N5" t="n">
-        <v>27.40141040718027</v>
+        <v>27.43925672043497</v>
       </c>
       <c r="O5" t="n">
-        <v>5.234635651808087</v>
+        <v>5.238249394638916</v>
       </c>
       <c r="P5" t="n">
-        <v>371.1886430250398</v>
+        <v>371.2124677502485</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26725,28 +26765,28 @@
         <v>0.0588</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2379268854062176</v>
+        <v>0.236917112758872</v>
       </c>
       <c r="J6" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="K6" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1803783814838817</v>
+        <v>0.1794920859369653</v>
       </c>
       <c r="M6" t="n">
-        <v>2.734342349463225</v>
+        <v>2.735118961679092</v>
       </c>
       <c r="N6" t="n">
-        <v>13.91815489114326</v>
+        <v>13.91166124541021</v>
       </c>
       <c r="O6" t="n">
-        <v>3.730704342499317</v>
+        <v>3.729833943409573</v>
       </c>
       <c r="P6" t="n">
-        <v>379.9180294112414</v>
+        <v>379.9284044019769</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26803,28 +26843,28 @@
         <v>0.06320000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1747101551838123</v>
+        <v>0.1736128695168793</v>
       </c>
       <c r="J7" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="K7" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05784526691367875</v>
+        <v>0.05732037112761268</v>
       </c>
       <c r="M7" t="n">
-        <v>4.117591068699532</v>
+        <v>4.115917529628609</v>
       </c>
       <c r="N7" t="n">
-        <v>26.9002558711761</v>
+        <v>26.87618491888274</v>
       </c>
       <c r="O7" t="n">
-        <v>5.186545658834606</v>
+        <v>5.184224620797477</v>
       </c>
       <c r="P7" t="n">
-        <v>359.8027821324202</v>
+        <v>359.8140562827534</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26862,7 +26902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H638"/>
+  <dimension ref="A1:H639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53657,6 +53697,48 @@
         </is>
       </c>
     </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>-36.309751590012155,174.79486615921664</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>-36.31047800272967,174.7948296327351</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>-36.31119637347873,174.79500916099758</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>-36.31190079322256,174.79521140997903</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>-36.3125479081536,174.79558568249558</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>-36.31328770797628,174.79564908218484</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0123/nzd0123.xlsx
+++ b/data/nzd0123/nzd0123.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H639"/>
+  <dimension ref="A1:H642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19608,6 +19608,96 @@
       <c r="H639" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>351.86</v>
+      </c>
+      <c r="C640" t="n">
+        <v>346.54</v>
+      </c>
+      <c r="D640" t="n">
+        <v>359.96</v>
+      </c>
+      <c r="E640" t="n">
+        <v>369.22</v>
+      </c>
+      <c r="F640" t="n">
+        <v>383.21</v>
+      </c>
+      <c r="G640" t="n">
+        <v>360.95</v>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>352.95</v>
+      </c>
+      <c r="C641" t="n">
+        <v>347.23</v>
+      </c>
+      <c r="D641" t="n">
+        <v>361.14</v>
+      </c>
+      <c r="E641" t="n">
+        <v>369.86</v>
+      </c>
+      <c r="F641" t="n">
+        <v>384.63</v>
+      </c>
+      <c r="G641" t="n">
+        <v>362.15</v>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:57+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>354.9</v>
+      </c>
+      <c r="C642" t="n">
+        <v>347.26</v>
+      </c>
+      <c r="D642" t="n">
+        <v>361.6</v>
+      </c>
+      <c r="E642" t="n">
+        <v>371.07</v>
+      </c>
+      <c r="F642" t="n">
+        <v>384.55</v>
+      </c>
+      <c r="G642" t="n">
+        <v>362.58</v>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -19622,7 +19712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B666"/>
+  <dimension ref="A1:B669"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26285,6 +26375,36 @@
       </c>
       <c r="B666" t="n">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="n">
+        <v>-0.21</v>
       </c>
     </row>
   </sheetData>
@@ -26453,28 +26573,28 @@
         <v>0.0654</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1094646308787722</v>
+        <v>0.1005359897309829</v>
       </c>
       <c r="J2" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="K2" t="n">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02734082725822695</v>
+        <v>0.02301027149824597</v>
       </c>
       <c r="M2" t="n">
-        <v>3.870142980548304</v>
+        <v>3.891404987501919</v>
       </c>
       <c r="N2" t="n">
-        <v>23.14652338184678</v>
+        <v>23.44565496964942</v>
       </c>
       <c r="O2" t="n">
-        <v>4.811083389616811</v>
+        <v>4.842071351152255</v>
       </c>
       <c r="P2" t="n">
-        <v>359.6598335954529</v>
+        <v>359.7518596593422</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26531,28 +26651,28 @@
         <v>0.0953</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2010910058217201</v>
+        <v>0.1903175733071991</v>
       </c>
       <c r="J3" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="K3" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05467339451625619</v>
+        <v>0.04904385455177407</v>
       </c>
       <c r="M3" t="n">
-        <v>5.231466882372998</v>
+        <v>5.251706103286025</v>
       </c>
       <c r="N3" t="n">
-        <v>37.90877898571216</v>
+        <v>38.31328404552458</v>
       </c>
       <c r="O3" t="n">
-        <v>6.15701055592015</v>
+        <v>6.189772535846902</v>
       </c>
       <c r="P3" t="n">
-        <v>352.9404085690507</v>
+        <v>353.0515163711958</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26609,28 +26729,28 @@
         <v>0.1104</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2709101186032515</v>
+        <v>0.2616771280412399</v>
       </c>
       <c r="J4" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="K4" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="L4" t="n">
-        <v>0.133092019670116</v>
+        <v>0.1246717687311675</v>
       </c>
       <c r="M4" t="n">
-        <v>4.085041245138786</v>
+        <v>4.104554430943041</v>
       </c>
       <c r="N4" t="n">
-        <v>25.91911088423081</v>
+        <v>26.22708639963417</v>
       </c>
       <c r="O4" t="n">
-        <v>5.091081504379086</v>
+        <v>5.121238756359068</v>
       </c>
       <c r="P4" t="n">
-        <v>363.3822697153264</v>
+        <v>363.4774878242151</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26687,28 +26807,28 @@
         <v>0.0921</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1821929597794094</v>
+        <v>0.1764722644607613</v>
       </c>
       <c r="J5" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="K5" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06155300352278059</v>
+        <v>0.05822854790843368</v>
       </c>
       <c r="M5" t="n">
-        <v>4.045774873749763</v>
+        <v>4.051635528146109</v>
       </c>
       <c r="N5" t="n">
-        <v>27.43925672043497</v>
+        <v>27.47756105403125</v>
       </c>
       <c r="O5" t="n">
-        <v>5.238249394638916</v>
+        <v>5.241904334688993</v>
       </c>
       <c r="P5" t="n">
-        <v>371.2124677502485</v>
+        <v>371.2714618808707</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26765,28 +26885,28 @@
         <v>0.0588</v>
       </c>
       <c r="I6" t="n">
-        <v>0.236917112758872</v>
+        <v>0.2349551780046259</v>
       </c>
       <c r="J6" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="K6" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1794920859369653</v>
+        <v>0.1784145257322656</v>
       </c>
       <c r="M6" t="n">
-        <v>2.735118961679092</v>
+        <v>2.732092786085831</v>
       </c>
       <c r="N6" t="n">
-        <v>13.91166124541021</v>
+        <v>13.86782288640753</v>
       </c>
       <c r="O6" t="n">
-        <v>3.729833943409573</v>
+        <v>3.723952589172898</v>
       </c>
       <c r="P6" t="n">
-        <v>379.9284044019769</v>
+        <v>379.9486345441648</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26843,28 +26963,28 @@
         <v>0.06320000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1736128695168793</v>
+        <v>0.171214269418974</v>
       </c>
       <c r="J7" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="K7" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05732037112761268</v>
+        <v>0.05634736178571587</v>
       </c>
       <c r="M7" t="n">
-        <v>4.115917529628609</v>
+        <v>4.106994533411497</v>
       </c>
       <c r="N7" t="n">
-        <v>26.87618491888274</v>
+        <v>26.7814562587338</v>
       </c>
       <c r="O7" t="n">
-        <v>5.184224620797477</v>
+        <v>5.175080314230283</v>
       </c>
       <c r="P7" t="n">
-        <v>359.8140562827534</v>
+        <v>359.8387891131911</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26902,7 +27022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H639"/>
+  <dimension ref="A1:H642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53739,6 +53859,132 @@
         </is>
       </c>
     </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>-36.30975161862386,174.79486515764202</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>-36.310478101032,174.79482685147585</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>-36.31119618035709,174.79501182290204</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>-36.31190012103291,174.79521555929136</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>-36.3125474408188,174.79558748538906</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>-36.31328783184767,174.79564866386468</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>-36.30975127210371,174.79487728782357</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>-36.3104778297174,174.79483452775133</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>-36.31119523084156,174.79502491059884</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>-36.311898988923716,174.79522254760673</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>-36.31254353719772,174.79560254485145</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>-36.31328411570558,174.795661213469</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:57+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>-36.30975065217928,174.79489898860666</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>-36.310477817921104,174.79483486150247</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>-36.311194860691046,174.79503001258223</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>-36.31189684852863,174.79523575988983</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>-36.31254375712009,174.79560169643108</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>-36.31328278408769,174.79566571041025</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0123/nzd0123.xlsx
+++ b/data/nzd0123/nzd0123.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H642"/>
+  <dimension ref="A1:H643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19696,6 +19696,36 @@
         <v>362.58</v>
       </c>
       <c r="H642" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>355.32</v>
+      </c>
+      <c r="C643" t="n">
+        <v>347.13</v>
+      </c>
+      <c r="D643" t="n">
+        <v>362.85</v>
+      </c>
+      <c r="E643" t="n">
+        <v>372.02</v>
+      </c>
+      <c r="F643" t="n">
+        <v>384.79</v>
+      </c>
+      <c r="G643" t="n">
+        <v>362.64</v>
+      </c>
+      <c r="H643" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -19712,7 +19742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B669"/>
+  <dimension ref="A1:B670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26405,6 +26435,16 @@
       </c>
       <c r="B669" t="n">
         <v>-0.21</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="n">
+        <v>-0.19</v>
       </c>
     </row>
   </sheetData>
@@ -26573,28 +26613,28 @@
         <v>0.0654</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1005359897309829</v>
+        <v>0.09826350251921763</v>
       </c>
       <c r="J2" t="n">
+        <v>642</v>
+      </c>
+      <c r="K2" t="n">
         <v>641</v>
       </c>
-      <c r="K2" t="n">
-        <v>640</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02301027149824597</v>
+        <v>0.02201067988052507</v>
       </c>
       <c r="M2" t="n">
-        <v>3.891404987501919</v>
+        <v>3.89526703828192</v>
       </c>
       <c r="N2" t="n">
-        <v>23.44565496964942</v>
+        <v>23.48708743336646</v>
       </c>
       <c r="O2" t="n">
-        <v>4.842071351152255</v>
+        <v>4.846347844858689</v>
       </c>
       <c r="P2" t="n">
-        <v>359.7518596593422</v>
+        <v>359.7753713076453</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26651,28 +26691,28 @@
         <v>0.0953</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1903175733071991</v>
+        <v>0.1868057989865287</v>
       </c>
       <c r="J3" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K3" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04904385455177407</v>
+        <v>0.04728007056758765</v>
       </c>
       <c r="M3" t="n">
-        <v>5.251706103286025</v>
+        <v>5.2580082779242</v>
       </c>
       <c r="N3" t="n">
-        <v>38.31328404552458</v>
+        <v>38.43954937629724</v>
       </c>
       <c r="O3" t="n">
-        <v>6.189772535846902</v>
+        <v>6.199963659272306</v>
       </c>
       <c r="P3" t="n">
-        <v>353.0515163711958</v>
+        <v>353.0878690468579</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26729,28 +26769,28 @@
         <v>0.1104</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2616771280412399</v>
+        <v>0.2592553222110952</v>
       </c>
       <c r="J4" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K4" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1246717687311675</v>
+        <v>0.122683190434319</v>
       </c>
       <c r="M4" t="n">
-        <v>4.104554430943041</v>
+        <v>4.108580122494324</v>
       </c>
       <c r="N4" t="n">
-        <v>26.22708639963417</v>
+        <v>26.27466555419412</v>
       </c>
       <c r="O4" t="n">
-        <v>5.121238756359068</v>
+        <v>5.125881929404355</v>
       </c>
       <c r="P4" t="n">
-        <v>363.4774878242151</v>
+        <v>363.5025575222709</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26807,28 +26847,28 @@
         <v>0.0921</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1764722644607613</v>
+        <v>0.1752146640618456</v>
       </c>
       <c r="J5" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K5" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05822854790843368</v>
+        <v>0.05759820518557524</v>
       </c>
       <c r="M5" t="n">
-        <v>4.051635528146109</v>
+        <v>4.050719629637082</v>
       </c>
       <c r="N5" t="n">
-        <v>27.47756105403125</v>
+        <v>27.45860696266258</v>
       </c>
       <c r="O5" t="n">
-        <v>5.241904334688993</v>
+        <v>5.240096083342612</v>
       </c>
       <c r="P5" t="n">
-        <v>371.2714618808707</v>
+        <v>371.2844801261336</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26885,28 +26925,28 @@
         <v>0.0588</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2349551780046259</v>
+        <v>0.2345127607609965</v>
       </c>
       <c r="J6" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K6" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1784145257322656</v>
+        <v>0.1783612392733845</v>
       </c>
       <c r="M6" t="n">
-        <v>2.732092786085831</v>
+        <v>2.730026952705041</v>
       </c>
       <c r="N6" t="n">
-        <v>13.86782288640753</v>
+        <v>13.84917306784379</v>
       </c>
       <c r="O6" t="n">
-        <v>3.723952589172898</v>
+        <v>3.721447711287072</v>
       </c>
       <c r="P6" t="n">
-        <v>379.9486345441648</v>
+        <v>379.9532142947684</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26963,28 +27003,28 @@
         <v>0.06320000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.171214269418974</v>
+        <v>0.17065906402686</v>
       </c>
       <c r="J7" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K7" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05634736178571587</v>
+        <v>0.05618536467182844</v>
       </c>
       <c r="M7" t="n">
-        <v>4.106994533411497</v>
+        <v>4.102972212680801</v>
       </c>
       <c r="N7" t="n">
-        <v>26.7814562587338</v>
+        <v>26.74438825947457</v>
       </c>
       <c r="O7" t="n">
-        <v>5.175080314230283</v>
+        <v>5.171497680505577</v>
       </c>
       <c r="P7" t="n">
-        <v>359.8387891131911</v>
+        <v>359.8445364077784</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27022,7 +27062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H642"/>
+  <dimension ref="A1:H643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53985,6 +54025,48 @@
         </is>
       </c>
     </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>-36.30975051865657,174.79490366262144</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>-36.31047786903839,174.79483341524767</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>-36.311193854846174,174.79504387666725</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>-36.311895168052175,174.79524613316943</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>-36.312543097352986,174.79560424169216</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>-36.31328259828052,174.7956663378904</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0123/nzd0123.xlsx
+++ b/data/nzd0123/nzd0123.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H643"/>
+  <dimension ref="A1:H644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19726,6 +19726,36 @@
         <v>362.64</v>
       </c>
       <c r="H643" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>357.06</v>
+      </c>
+      <c r="C644" t="n">
+        <v>347.11</v>
+      </c>
+      <c r="D644" t="n">
+        <v>364.16</v>
+      </c>
+      <c r="E644" t="n">
+        <v>373.04</v>
+      </c>
+      <c r="F644" t="n">
+        <v>386.32</v>
+      </c>
+      <c r="G644" t="n">
+        <v>363.67</v>
+      </c>
+      <c r="H644" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -19742,7 +19772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B670"/>
+  <dimension ref="A1:B671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26445,6 +26475,16 @@
       </c>
       <c r="B670" t="n">
         <v>-0.19</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="n">
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
@@ -26613,28 +26653,28 @@
         <v>0.0654</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09826350251921763</v>
+        <v>0.09655963377930521</v>
       </c>
       <c r="J2" t="n">
+        <v>643</v>
+      </c>
+      <c r="K2" t="n">
         <v>642</v>
       </c>
-      <c r="K2" t="n">
-        <v>641</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02201067988052507</v>
+        <v>0.02130655483891042</v>
       </c>
       <c r="M2" t="n">
-        <v>3.89526703828192</v>
+        <v>3.896601962497625</v>
       </c>
       <c r="N2" t="n">
-        <v>23.48708743336646</v>
+        <v>23.49440278961872</v>
       </c>
       <c r="O2" t="n">
-        <v>4.846347844858689</v>
+        <v>4.847102514865837</v>
       </c>
       <c r="P2" t="n">
-        <v>359.7753713076453</v>
+        <v>359.7930320764484</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26691,28 +26731,28 @@
         <v>0.0953</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1868057989865287</v>
+        <v>0.1833077503346564</v>
       </c>
       <c r="J3" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="K3" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04728007056758765</v>
+        <v>0.04555472334171651</v>
       </c>
       <c r="M3" t="n">
-        <v>5.2580082779242</v>
+        <v>5.26424108414251</v>
       </c>
       <c r="N3" t="n">
-        <v>38.43954937629724</v>
+        <v>38.56445039686302</v>
       </c>
       <c r="O3" t="n">
-        <v>6.199963659272306</v>
+        <v>6.210028212243727</v>
       </c>
       <c r="P3" t="n">
-        <v>353.0878690468579</v>
+        <v>353.1241455563211</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26769,28 +26809,28 @@
         <v>0.1104</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2592553222110952</v>
+        <v>0.2572651446943298</v>
       </c>
       <c r="J4" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="K4" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L4" t="n">
-        <v>0.122683190434319</v>
+        <v>0.1211772981535507</v>
       </c>
       <c r="M4" t="n">
-        <v>4.108580122494324</v>
+        <v>4.110829502020417</v>
       </c>
       <c r="N4" t="n">
-        <v>26.27466555419412</v>
+        <v>26.29358320631199</v>
       </c>
       <c r="O4" t="n">
-        <v>5.125881929404355</v>
+        <v>5.127726904419929</v>
       </c>
       <c r="P4" t="n">
-        <v>363.5025575222709</v>
+        <v>363.5231966558867</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26847,28 +26887,28 @@
         <v>0.0921</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1752146640618456</v>
+        <v>0.1742898267430611</v>
       </c>
       <c r="J5" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="K5" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05759820518557524</v>
+        <v>0.05719608721575542</v>
       </c>
       <c r="M5" t="n">
-        <v>4.050719629637082</v>
+        <v>4.048364562671423</v>
       </c>
       <c r="N5" t="n">
-        <v>27.45860696266258</v>
+        <v>27.42881243112986</v>
       </c>
       <c r="O5" t="n">
-        <v>5.240096083342612</v>
+        <v>5.237252374206331</v>
       </c>
       <c r="P5" t="n">
-        <v>371.2844801261336</v>
+        <v>371.2940711504691</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26925,28 +26965,28 @@
         <v>0.0588</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2345127607609965</v>
+        <v>0.2345613957050905</v>
       </c>
       <c r="J6" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="K6" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1783612392733845</v>
+        <v>0.1789533255622435</v>
       </c>
       <c r="M6" t="n">
-        <v>2.730026952705041</v>
+        <v>2.726011879629434</v>
       </c>
       <c r="N6" t="n">
-        <v>13.84917306784379</v>
+        <v>13.82767039628085</v>
       </c>
       <c r="O6" t="n">
-        <v>3.721447711287072</v>
+        <v>3.718557569311096</v>
       </c>
       <c r="P6" t="n">
-        <v>379.9532142947684</v>
+        <v>379.9527099261375</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27003,28 +27043,28 @@
         <v>0.06320000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.17065906402686</v>
+        <v>0.1704364966523121</v>
       </c>
       <c r="J7" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="K7" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05618536467182844</v>
+        <v>0.05623760955812007</v>
       </c>
       <c r="M7" t="n">
-        <v>4.102972212680801</v>
+        <v>4.097537844538161</v>
       </c>
       <c r="N7" t="n">
-        <v>26.74438825947457</v>
+        <v>26.70354276882276</v>
       </c>
       <c r="O7" t="n">
-        <v>5.171497680505577</v>
+        <v>5.167547074659577</v>
       </c>
       <c r="P7" t="n">
-        <v>359.8445364077784</v>
+        <v>359.8468445424766</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27062,7 +27102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H643"/>
+  <dimension ref="A1:H644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54067,6 +54107,48 @@
         </is>
       </c>
     </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>-36.30974996548916,174.79492302639662</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>-36.310477876902574,174.79483319274692</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>-36.31119280071903,174.79505840622792</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>-36.311893363750144,174.7952572707954</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>-36.31253889133641,174.79562046773069</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>-36.313279408590425,174.7956771096327</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0123/nzd0123.xlsx
+++ b/data/nzd0123/nzd0123.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H644"/>
+  <dimension ref="A1:H647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19756,6 +19756,96 @@
         <v>363.67</v>
       </c>
       <c r="H644" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>357.49</v>
+      </c>
+      <c r="C645" t="n">
+        <v>346.99</v>
+      </c>
+      <c r="D645" t="n">
+        <v>363.76</v>
+      </c>
+      <c r="E645" t="n">
+        <v>372.13</v>
+      </c>
+      <c r="F645" t="n">
+        <v>386.08</v>
+      </c>
+      <c r="G645" t="n">
+        <v>363.5</v>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>356.98</v>
+      </c>
+      <c r="C646" t="n">
+        <v>347.42</v>
+      </c>
+      <c r="D646" t="n">
+        <v>364.07</v>
+      </c>
+      <c r="E646" t="n">
+        <v>372.36</v>
+      </c>
+      <c r="F646" t="n">
+        <v>386.21</v>
+      </c>
+      <c r="G646" t="n">
+        <v>363.66</v>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>357.57</v>
+      </c>
+      <c r="C647" t="n">
+        <v>347.96</v>
+      </c>
+      <c r="D647" t="n">
+        <v>364.58</v>
+      </c>
+      <c r="E647" t="n">
+        <v>371.81</v>
+      </c>
+      <c r="F647" t="n">
+        <v>386.14</v>
+      </c>
+      <c r="G647" t="n">
+        <v>363.75</v>
+      </c>
+      <c r="H647" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -19772,7 +19862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B671"/>
+  <dimension ref="A1:B674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26484,6 +26574,36 @@
         </is>
       </c>
       <c r="B671" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="n">
         <v>-0.6</v>
       </c>
     </row>
@@ -26653,28 +26773,28 @@
         <v>0.0654</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09655963377930521</v>
+        <v>0.09177817913480463</v>
       </c>
       <c r="J2" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="K2" t="n">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02130655483891042</v>
+        <v>0.01940165201578725</v>
       </c>
       <c r="M2" t="n">
-        <v>3.896601962497625</v>
+        <v>3.899145833337149</v>
       </c>
       <c r="N2" t="n">
-        <v>23.49440278961872</v>
+        <v>23.50061836639974</v>
       </c>
       <c r="O2" t="n">
-        <v>4.847102514865837</v>
+        <v>4.847743636621035</v>
       </c>
       <c r="P2" t="n">
-        <v>359.7930320764484</v>
+        <v>359.8427838649502</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26731,28 +26851,28 @@
         <v>0.0953</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1833077503346564</v>
+        <v>0.1732536944364142</v>
       </c>
       <c r="J3" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="K3" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04555472334171651</v>
+        <v>0.04080429649241657</v>
       </c>
       <c r="M3" t="n">
-        <v>5.26424108414251</v>
+        <v>5.280913625015964</v>
       </c>
       <c r="N3" t="n">
-        <v>38.56445039686302</v>
+        <v>38.89444437132364</v>
       </c>
       <c r="O3" t="n">
-        <v>6.210028212243727</v>
+        <v>6.236541058256864</v>
       </c>
       <c r="P3" t="n">
-        <v>353.1241455563211</v>
+        <v>353.2288103356163</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26809,28 +26929,28 @@
         <v>0.1104</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2572651446943298</v>
+        <v>0.2513242373009074</v>
       </c>
       <c r="J4" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="K4" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1211772981535507</v>
+        <v>0.1167130164813395</v>
       </c>
       <c r="M4" t="n">
-        <v>4.110829502020417</v>
+        <v>4.117585164710722</v>
       </c>
       <c r="N4" t="n">
-        <v>26.29358320631199</v>
+        <v>26.34950836797399</v>
       </c>
       <c r="O4" t="n">
-        <v>5.127726904419929</v>
+        <v>5.133177219614962</v>
       </c>
       <c r="P4" t="n">
-        <v>363.5231966558867</v>
+        <v>363.5850415265695</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26887,28 +27007,28 @@
         <v>0.0921</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1742898267430611</v>
+        <v>0.1706381640197555</v>
       </c>
       <c r="J5" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="K5" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05719608721575542</v>
+        <v>0.05539487058729675</v>
       </c>
       <c r="M5" t="n">
-        <v>4.048364562671423</v>
+        <v>4.044925379716445</v>
       </c>
       <c r="N5" t="n">
-        <v>27.42881243112986</v>
+        <v>27.36870950230059</v>
       </c>
       <c r="O5" t="n">
-        <v>5.237252374206331</v>
+        <v>5.231511206362899</v>
       </c>
       <c r="P5" t="n">
-        <v>371.2940711504691</v>
+        <v>371.3320892243567</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26965,28 +27085,28 @@
         <v>0.0588</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2345613957050905</v>
+        <v>0.2345167221344814</v>
       </c>
       <c r="J6" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="K6" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1789533255622435</v>
+        <v>0.1805042413482433</v>
       </c>
       <c r="M6" t="n">
-        <v>2.726011879629434</v>
+        <v>2.713637519519374</v>
       </c>
       <c r="N6" t="n">
-        <v>13.82767039628085</v>
+        <v>13.76347704818764</v>
       </c>
       <c r="O6" t="n">
-        <v>3.718557569311096</v>
+        <v>3.709916043280176</v>
       </c>
       <c r="P6" t="n">
-        <v>379.9527099261375</v>
+        <v>379.953174908558</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27043,28 +27163,28 @@
         <v>0.06320000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1704364966523121</v>
+        <v>0.169723993463294</v>
       </c>
       <c r="J7" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="K7" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05623760955812007</v>
+        <v>0.05636652188374025</v>
       </c>
       <c r="M7" t="n">
-        <v>4.097537844538161</v>
+        <v>4.081499697966741</v>
       </c>
       <c r="N7" t="n">
-        <v>26.70354276882276</v>
+        <v>26.58213257667822</v>
       </c>
       <c r="O7" t="n">
-        <v>5.167547074659577</v>
+        <v>5.155786319920388</v>
       </c>
       <c r="P7" t="n">
-        <v>359.8468445424766</v>
+        <v>359.8542610822782</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27102,7 +27222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H644"/>
+  <dimension ref="A1:H647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54149,6 +54269,132 @@
         </is>
       </c>
     </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>-36.30974982878637,174.7949278116973</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>-36.31047792408775,174.79483185774248</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>-36.311193122590105,174.7950539697209</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>-36.31189497347063,174.79524733428596</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>-36.31253955110386,174.79561792246986</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>-36.3132799350442,174.7956753317724</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>-36.309749990922214,174.79492213610808</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>-36.3104777550075,174.79483664150837</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>-36.31119287314004,174.79505740801383</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>-36.31189456661827,174.79524984571148</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>-36.31253919372984,174.7956193011528</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>-36.313279439558286,174.7956770050527</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>-36.309749803353284,174.7949287019858</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>-36.31047754267387,174.79484264902825</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>-36.31119246275424,174.79506306456022</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>-36.31189553952599,174.79524384012873</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>-36.312539386161994,174.7956185587851</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>-36.31327916084745,174.79567794627286</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0123/nzd0123.xlsx
+++ b/data/nzd0123/nzd0123.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H647"/>
+  <dimension ref="A1:H652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19848,6 +19848,156 @@
       <c r="H647" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>357.05</v>
+      </c>
+      <c r="C648" t="n">
+        <v>348.29</v>
+      </c>
+      <c r="D648" t="n">
+        <v>365.09</v>
+      </c>
+      <c r="E648" t="n">
+        <v>371.79</v>
+      </c>
+      <c r="F648" t="n">
+        <v>385.87</v>
+      </c>
+      <c r="G648" t="n">
+        <v>363.16</v>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="n">
+        <v>356.42</v>
+      </c>
+      <c r="C649" t="n">
+        <v>347.72</v>
+      </c>
+      <c r="D649" t="n">
+        <v>364.44</v>
+      </c>
+      <c r="E649" t="n">
+        <v>371.22</v>
+      </c>
+      <c r="F649" t="n">
+        <v>385.59</v>
+      </c>
+      <c r="G649" t="n">
+        <v>362.65</v>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:05+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="n">
+        <v>355.32</v>
+      </c>
+      <c r="C650" t="n">
+        <v>346.82</v>
+      </c>
+      <c r="D650" t="n">
+        <v>363.44</v>
+      </c>
+      <c r="E650" t="n">
+        <v>370.65</v>
+      </c>
+      <c r="F650" t="n">
+        <v>385.38</v>
+      </c>
+      <c r="G650" t="n">
+        <v>363.1</v>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="n">
+        <v>354.5</v>
+      </c>
+      <c r="C651" t="n">
+        <v>345.29</v>
+      </c>
+      <c r="D651" t="n">
+        <v>363.43</v>
+      </c>
+      <c r="E651" t="n">
+        <v>370.3</v>
+      </c>
+      <c r="F651" t="n">
+        <v>384.9</v>
+      </c>
+      <c r="G651" t="n">
+        <v>362.59</v>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="n">
+        <v>354.45</v>
+      </c>
+      <c r="C652" t="n">
+        <v>345.02</v>
+      </c>
+      <c r="D652" t="n">
+        <v>362.62</v>
+      </c>
+      <c r="E652" t="n">
+        <v>370.11</v>
+      </c>
+      <c r="F652" t="n">
+        <v>384.2</v>
+      </c>
+      <c r="G652" t="n">
+        <v>361.69</v>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -19862,7 +20012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B674"/>
+  <dimension ref="A1:B679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26605,6 +26755,56 @@
       </c>
       <c r="B674" t="n">
         <v>-0.6</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="n">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="n">
+        <v>-0.03</v>
       </c>
     </row>
   </sheetData>
@@ -26773,28 +26973,28 @@
         <v>0.0654</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09177817913480463</v>
+        <v>0.08125469474567693</v>
       </c>
       <c r="J2" t="n">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="K2" t="n">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01940165201578725</v>
+        <v>0.01531792849427127</v>
       </c>
       <c r="M2" t="n">
-        <v>3.899145833337149</v>
+        <v>3.914038840956765</v>
       </c>
       <c r="N2" t="n">
-        <v>23.50061836639974</v>
+        <v>23.66906398543131</v>
       </c>
       <c r="O2" t="n">
-        <v>4.847743636621035</v>
+        <v>4.865086225898911</v>
       </c>
       <c r="P2" t="n">
-        <v>359.8427838649502</v>
+        <v>359.9526737281636</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26851,28 +27051,28 @@
         <v>0.0953</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1732536944364142</v>
+        <v>0.155737970924692</v>
       </c>
       <c r="J3" t="n">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="K3" t="n">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04080429649241657</v>
+        <v>0.03302272873799306</v>
       </c>
       <c r="M3" t="n">
-        <v>5.280913625015964</v>
+        <v>5.311623227727149</v>
       </c>
       <c r="N3" t="n">
-        <v>38.89444437132364</v>
+        <v>39.55143873387996</v>
       </c>
       <c r="O3" t="n">
-        <v>6.236541058256864</v>
+        <v>6.288993459519572</v>
       </c>
       <c r="P3" t="n">
-        <v>353.2288103356163</v>
+        <v>353.4118028271528</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26929,28 +27129,28 @@
         <v>0.1104</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2513242373009074</v>
+        <v>0.2412008084897165</v>
       </c>
       <c r="J4" t="n">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="K4" t="n">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1167130164813395</v>
+        <v>0.1090580898939513</v>
       </c>
       <c r="M4" t="n">
-        <v>4.117585164710722</v>
+        <v>4.130166061702617</v>
       </c>
       <c r="N4" t="n">
-        <v>26.34950836797399</v>
+        <v>26.4678687953204</v>
       </c>
       <c r="O4" t="n">
-        <v>5.133177219614962</v>
+        <v>5.144693265426074</v>
       </c>
       <c r="P4" t="n">
-        <v>363.5850415265695</v>
+        <v>363.6908051588106</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27007,28 +27207,28 @@
         <v>0.0921</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1706381640197555</v>
+        <v>0.1627236299723422</v>
       </c>
       <c r="J5" t="n">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="K5" t="n">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05539487058729675</v>
+        <v>0.05115035773042087</v>
       </c>
       <c r="M5" t="n">
-        <v>4.044925379716445</v>
+        <v>4.046732923065557</v>
       </c>
       <c r="N5" t="n">
-        <v>27.36870950230059</v>
+        <v>27.35394209561948</v>
       </c>
       <c r="O5" t="n">
-        <v>5.231511206362899</v>
+        <v>5.230099625783383</v>
       </c>
       <c r="P5" t="n">
-        <v>371.3320892243567</v>
+        <v>371.4147753748242</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27085,28 +27285,28 @@
         <v>0.0588</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2345167221344814</v>
+        <v>0.2329196716244815</v>
       </c>
       <c r="J6" t="n">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="K6" t="n">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1805042413482433</v>
+        <v>0.1810254562429204</v>
       </c>
       <c r="M6" t="n">
-        <v>2.713637519519374</v>
+        <v>2.700579318916871</v>
       </c>
       <c r="N6" t="n">
-        <v>13.76347704818764</v>
+        <v>13.66825407909688</v>
       </c>
       <c r="O6" t="n">
-        <v>3.709916043280176</v>
+        <v>3.697060194140323</v>
       </c>
       <c r="P6" t="n">
-        <v>379.953174908558</v>
+        <v>379.9698646521146</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27163,28 +27363,28 @@
         <v>0.06320000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.169723993463294</v>
+        <v>0.1670026169544787</v>
       </c>
       <c r="J7" t="n">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="K7" t="n">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05636652188374025</v>
+        <v>0.05555730430522632</v>
       </c>
       <c r="M7" t="n">
-        <v>4.081499697966741</v>
+        <v>4.061476475926731</v>
       </c>
       <c r="N7" t="n">
-        <v>26.58213257667822</v>
+        <v>26.40285880245741</v>
       </c>
       <c r="O7" t="n">
-        <v>5.155786319920388</v>
+        <v>5.138371220771949</v>
       </c>
       <c r="P7" t="n">
-        <v>359.8542610822782</v>
+        <v>359.8826947021213</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27222,7 +27422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H647"/>
+  <dimension ref="A1:H652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54395,6 +54595,216 @@
         </is>
       </c>
     </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>-36.309749968668285,174.79492291511053</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>-36.310477412914295,174.7948463202904</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>-36.31119205236816,174.79506872110656</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>-36.311895574904455,174.79524362174388</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>-36.312540128400336,174.79561569536662</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>-36.31328098795166,174.79567177605168</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>-36.30975016895339,174.79491590408853</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>-36.31047763704441,174.79483997901943</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>-36.311192575409194,174.7950615117828</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>-36.31189658319032,174.7952373977761</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>-36.312540898128894,174.79561272589555</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>-36.31328256731266,174.79566644247046</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:05+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>-36.30975051865657,174.79490366262144</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>-36.31047799093338,174.7948299664862</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>-36.31119338008684,174.79505042051525</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>-36.31189759147586,174.7952311738082</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>-36.312541475425284,174.7956104987922</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>-36.31328117375885,174.79567114857156</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>-36.30975077934358,174.79489453716403</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>-36.3104785925427,174.79481294517944</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>-36.31119338813362,174.79505030960254</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>-36.3118982105984,174.7952273520734</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>-36.312542794959704,174.79560540827018</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>-36.31328275311982,174.7956658149903</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>-36.30975079523912,174.79489398073372</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>-36.31047869870882,174.79480994141937</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>-36.31119403992175,174.79504132567564</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>-36.31189854669344,174.79522527741733</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>-36.31254471928036,174.7955979845919</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>-36.313285540226865,174.7956564027875</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0123/nzd0123.xlsx
+++ b/data/nzd0123/nzd0123.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H652"/>
+  <dimension ref="A1:H657"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19996,6 +19996,156 @@
         <v>361.69</v>
       </c>
       <c r="H652" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="n">
+        <v>354.45</v>
+      </c>
+      <c r="C653" t="n">
+        <v>345.02</v>
+      </c>
+      <c r="D653" t="n">
+        <v>362.62</v>
+      </c>
+      <c r="E653" t="n">
+        <v>369.57</v>
+      </c>
+      <c r="F653" t="n">
+        <v>382.76</v>
+      </c>
+      <c r="G653" t="n">
+        <v>360.14</v>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="n">
+        <v>354.21</v>
+      </c>
+      <c r="C654" t="n">
+        <v>345.11</v>
+      </c>
+      <c r="D654" t="n">
+        <v>363.99</v>
+      </c>
+      <c r="E654" t="n">
+        <v>370.72</v>
+      </c>
+      <c r="F654" t="n">
+        <v>383.87</v>
+      </c>
+      <c r="G654" t="n">
+        <v>361</v>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="n">
+        <v>353.75</v>
+      </c>
+      <c r="C655" t="n">
+        <v>345.11</v>
+      </c>
+      <c r="D655" t="n">
+        <v>364.2</v>
+      </c>
+      <c r="E655" t="n">
+        <v>371.51</v>
+      </c>
+      <c r="F655" t="n">
+        <v>384.36</v>
+      </c>
+      <c r="G655" t="n">
+        <v>361.52</v>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="n">
+        <v>353.62</v>
+      </c>
+      <c r="C656" t="n">
+        <v>345.79</v>
+      </c>
+      <c r="D656" t="n">
+        <v>364.22</v>
+      </c>
+      <c r="E656" t="n">
+        <v>372.11</v>
+      </c>
+      <c r="F656" t="n">
+        <v>384.54</v>
+      </c>
+      <c r="G656" t="n">
+        <v>362.14</v>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="n">
+        <v>352.93</v>
+      </c>
+      <c r="C657" t="n">
+        <v>345.46</v>
+      </c>
+      <c r="D657" t="n">
+        <v>364.11</v>
+      </c>
+      <c r="E657" t="n">
+        <v>372.36</v>
+      </c>
+      <c r="F657" t="n">
+        <v>384.5</v>
+      </c>
+      <c r="G657" t="n">
+        <v>362.16</v>
+      </c>
+      <c r="H657" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20012,7 +20162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B679"/>
+  <dimension ref="A1:B684"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26805,6 +26955,56 @@
       </c>
       <c r="B679" t="n">
         <v>-0.03</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="n">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="n">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>-0.79</v>
       </c>
     </row>
   </sheetData>
@@ -26973,28 +27173,28 @@
         <v>0.0654</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08125469474567693</v>
+        <v>0.06844215302163517</v>
       </c>
       <c r="J2" t="n">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="K2" t="n">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01531792849427127</v>
+        <v>0.01087171625546346</v>
       </c>
       <c r="M2" t="n">
-        <v>3.914038840956765</v>
+        <v>3.938668437838596</v>
       </c>
       <c r="N2" t="n">
-        <v>23.66906398543131</v>
+        <v>24.00788435733849</v>
       </c>
       <c r="O2" t="n">
-        <v>4.865086225898911</v>
+        <v>4.899784113339943</v>
       </c>
       <c r="P2" t="n">
-        <v>359.9526737281636</v>
+        <v>360.0870903970744</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27051,28 +27251,28 @@
         <v>0.0953</v>
       </c>
       <c r="I3" t="n">
-        <v>0.155737970924692</v>
+        <v>0.1368557242110008</v>
       </c>
       <c r="J3" t="n">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="K3" t="n">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03302272873799306</v>
+        <v>0.02543275690934144</v>
       </c>
       <c r="M3" t="n">
-        <v>5.311623227727149</v>
+        <v>5.347758848070584</v>
       </c>
       <c r="N3" t="n">
-        <v>39.55143873387996</v>
+        <v>40.37259144749105</v>
       </c>
       <c r="O3" t="n">
-        <v>6.288993459519572</v>
+        <v>6.353942984280788</v>
       </c>
       <c r="P3" t="n">
-        <v>353.4118028271528</v>
+        <v>353.6099794596861</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27129,28 +27329,28 @@
         <v>0.1104</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2412008084897165</v>
+        <v>0.2314806661982385</v>
       </c>
       <c r="J4" t="n">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="K4" t="n">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1090580898939513</v>
+        <v>0.101898101507276</v>
       </c>
       <c r="M4" t="n">
-        <v>4.130166061702617</v>
+        <v>4.140909012499068</v>
       </c>
       <c r="N4" t="n">
-        <v>26.4678687953204</v>
+        <v>26.56631341249357</v>
       </c>
       <c r="O4" t="n">
-        <v>5.144693265426074</v>
+        <v>5.154251974098043</v>
       </c>
       <c r="P4" t="n">
-        <v>363.6908051588106</v>
+        <v>363.7928169668475</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27207,28 +27407,28 @@
         <v>0.0921</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1627236299723422</v>
+        <v>0.1557794045686093</v>
       </c>
       <c r="J5" t="n">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="K5" t="n">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05115035773042087</v>
+        <v>0.04761363380344918</v>
       </c>
       <c r="M5" t="n">
-        <v>4.046732923065557</v>
+        <v>4.04457392631557</v>
       </c>
       <c r="N5" t="n">
-        <v>27.35394209561948</v>
+        <v>27.30512972029021</v>
       </c>
       <c r="O5" t="n">
-        <v>5.230099625783383</v>
+        <v>5.225431055931195</v>
       </c>
       <c r="P5" t="n">
-        <v>371.4147753748242</v>
+        <v>371.4876444667024</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27285,28 +27485,28 @@
         <v>0.0588</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2329196716244815</v>
+        <v>0.2295343364373979</v>
       </c>
       <c r="J6" t="n">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="K6" t="n">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1810254562429204</v>
+        <v>0.1788906227387925</v>
       </c>
       <c r="M6" t="n">
-        <v>2.700579318916871</v>
+        <v>2.696437581420827</v>
       </c>
       <c r="N6" t="n">
-        <v>13.66825407909688</v>
+        <v>13.60351319053477</v>
       </c>
       <c r="O6" t="n">
-        <v>3.697060194140323</v>
+        <v>3.688294075929246</v>
       </c>
       <c r="P6" t="n">
-        <v>379.9698646521146</v>
+        <v>380.0053872817755</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27363,28 +27563,28 @@
         <v>0.06320000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1670026169544787</v>
+        <v>0.1624472014660545</v>
       </c>
       <c r="J7" t="n">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="K7" t="n">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05555730430522632</v>
+        <v>0.0534826822469483</v>
       </c>
       <c r="M7" t="n">
-        <v>4.061476475926731</v>
+        <v>4.0494674434903</v>
       </c>
       <c r="N7" t="n">
-        <v>26.40285880245741</v>
+        <v>26.27133700249238</v>
       </c>
       <c r="O7" t="n">
-        <v>5.138371220771949</v>
+        <v>5.125557238241749</v>
       </c>
       <c r="P7" t="n">
-        <v>359.8826947021213</v>
+        <v>359.9304956507612</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27422,7 +27622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H652"/>
+  <dimension ref="A1:H657"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54805,6 +55005,216 @@
         </is>
       </c>
     </row>
+    <row r="653">
+      <c r="A653" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>-36.30975079523912,174.79489398073372</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>-36.31047869870882,174.79480994141937</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>-36.31119403992175,174.79504132567564</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>-36.311899501910744,174.79521938102636</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>-36.31254867788144,174.7955827130239</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>-36.313290340242844,174.79564019288105</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>-36.309750871537595,174.7948913098681</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>-36.31047866332012,174.79481094267274</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>-36.31119293751426,174.79505652071242</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>-36.31189746765133,174.79523193815513</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>-36.31254562645994,174.7955944848577</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>-36.31328767700844,174.79564918676488</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>-36.30975101777621,174.794886190709</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>-36.31047866332012,174.79481094267274</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>-36.31119276853192,174.79505884987861</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>-36.31189607020281,174.79524056435622</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>-36.31254427943568,174.79559968143266</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>-36.313286066680334,174.7956546249269</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>-36.30975105910448,174.79488474399014</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>-36.31047839593861,174.79481850769804</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>-36.31119275243836,174.79505907170395</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>-36.31189500884909,174.79524711590113</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>-36.31254378461038,174.79560159037854</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>-36.313284146673446,174.79566110888896</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>-36.309751278461896,174.79487706525143</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>-36.31047852569735,174.79481483643576</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>-36.31119284095293,174.79505785166455</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>-36.31189456661827,174.79524984571148</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>-36.31254389457157,174.79560116616832</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>-36.313284084737724,174.79566131804904</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
